--- a/data/trans_dic/P62A$viudedad-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 16,73</t>
+          <t>9,77; 16,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,28; 58,91</t>
+          <t>49,04; 58,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,01; 56,73</t>
+          <t>48,08; 56,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,81; 51,78</t>
+          <t>40,19; 50,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,3</t>
+          <t>4,53; 8,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,97; 28,47</t>
+          <t>22,84; 28,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,52; 29,14</t>
+          <t>23,37; 28,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,63; 25,53</t>
+          <t>19,56; 25,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,04</t>
+          <t>7,37; 10,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 24,17</t>
+          <t>16,97; 24,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,64; 49,42</t>
+          <t>28,66; 49,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 29,8</t>
+          <t>15,62; 28,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,15; 31,03</t>
+          <t>19,54; 31,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 12,59</t>
+          <t>2,28; 11,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 18,07</t>
+          <t>9,14; 18,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,48</t>
+          <t>5,96; 11,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,73</t>
+          <t>7,46; 12,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 17,53</t>
+          <t>6,29; 17,36</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 16,79</t>
+          <t>5,26; 17,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 28,71</t>
+          <t>6,56; 30,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 28,04</t>
+          <t>2,79; 28,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 20,43</t>
+          <t>3,7; 18,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 14,52</t>
+          <t>4,84; 14,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 13,44</t>
+          <t>2,26; 12,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,26</t>
+          <t>1,24; 13,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,84</t>
+          <t>1,66; 9,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,92</t>
+          <t>6,35; 14,1</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 18,65</t>
+          <t>13,86; 19,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,97; 53,3</t>
+          <t>45,58; 53,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,72; 47,0</t>
+          <t>39,82; 47,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,06; 39,6</t>
+          <t>31,8; 39,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,89</t>
+          <t>3,22; 8,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,62; 24,17</t>
+          <t>19,55; 23,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,25; 22,59</t>
+          <t>18,11; 22,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 18,27</t>
+          <t>14,43; 18,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 13,17</t>
+          <t>7,38; 13,1</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6823</t>
+          <t>0; 6869</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 10170</t>
+          <t>0; 12750</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1819</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29644; 50007</t>
+          <t>29204; 48366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>221683; 264990</t>
+          <t>220631; 265020</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>257708; 304503</t>
+          <t>258050; 304159</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>173642; 220302</t>
+          <t>170990; 215111</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16662; 31334</t>
+          <t>17094; 30479</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>220573; 273442</t>
+          <t>219338; 274510</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>255355; 316408</t>
+          <t>253722; 312421</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170010; 221070</t>
+          <t>169348; 220765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50395; 74672</t>
+          <t>49849; 74153</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1914</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5048</t>
+          <t>0; 5191</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66984; 94802</t>
+          <t>66550; 96288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24346; 42006</t>
+          <t>24356; 42060</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27024; 50856</t>
+          <t>26653; 49456</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49280; 79870</t>
+          <t>50293; 80848</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10726; 60886</t>
+          <t>11046; 57767</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23261; 45482</t>
+          <t>22988; 45611</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27529; 51197</t>
+          <t>26571; 52539</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49139; 82110</t>
+          <t>48086; 83388</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56508; 153523</t>
+          <t>55077; 152015</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2110</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2234</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2041</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6117; 18190</t>
+          <t>5701; 18463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2285; 11837</t>
+          <t>2706; 12473</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1101; 9977</t>
+          <t>994; 10162</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1960; 10782</t>
+          <t>1953; 9927</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3624; 10740</t>
+          <t>3578; 11077</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2094; 13696</t>
+          <t>2301; 12817</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>991; 9140</t>
+          <t>1009; 10786</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2000; 10794</t>
+          <t>2024; 11353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11894; 25387</t>
+          <t>11575; 25701</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6720</t>
+          <t>0; 6964</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 12351</t>
+          <t>0; 12325</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6917</t>
+          <t>0; 4697</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>112096; 149063</t>
+          <t>110799; 152098</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>259080; 307049</t>
+          <t>262575; 309304</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>295134; 349169</t>
+          <t>295850; 349342</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>235814; 291293</t>
+          <t>233960; 291863</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32023; 83126</t>
+          <t>30141; 82751</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>257740; 317638</t>
+          <t>256818; 314441</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>294397; 364316</t>
+          <t>292184; 359494</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>232831; 298327</t>
+          <t>235693; 299146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>129410; 228385</t>
+          <t>128103; 227177</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$viudedad-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 16,18</t>
+          <t>9,3; 15,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,04; 58,91</t>
+          <t>49,23; 58,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,08; 56,67</t>
+          <t>47,81; 56,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,19; 50,56</t>
+          <t>40,28; 50,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,07</t>
+          <t>4,26; 7,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,84; 28,58</t>
+          <t>22,88; 28,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,37; 28,77</t>
+          <t>23,33; 28,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,56; 25,49</t>
+          <t>19,44; 25,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,96</t>
+          <t>7,07; 10,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,97; 24,55</t>
+          <t>16,17; 23,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,66; 49,48</t>
+          <t>27,24; 49,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 28,98</t>
+          <t>15,54; 29,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,54; 31,41</t>
+          <t>18,71; 30,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 11,94</t>
+          <t>8,37; 14,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 18,13</t>
+          <t>9,12; 17,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,78</t>
+          <t>6,11; 11,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,93</t>
+          <t>7,66; 12,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 17,36</t>
+          <t>13,78; 18,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 17,04</t>
+          <t>5,18; 15,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 30,25</t>
+          <t>6,43; 28,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 28,57</t>
+          <t>2,87; 25,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 18,81</t>
+          <t>2,17; 19,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 14,97</t>
+          <t>5,01; 14,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 12,58</t>
+          <t>2,24; 12,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 13,28</t>
+          <t>1,21; 11,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,3</t>
+          <t>1,57; 9,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 14,1</t>
+          <t>6,27; 13,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 19,03</t>
+          <t>13,25; 17,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,58; 53,69</t>
+          <t>45,35; 53,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,82; 47,02</t>
+          <t>39,8; 47,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,8; 39,68</t>
+          <t>32,19; 39,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,85</t>
+          <t>6,92; 9,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 23,93</t>
+          <t>19,41; 23,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 22,29</t>
+          <t>18,1; 22,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 18,32</t>
+          <t>14,32; 18,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 13,1</t>
+          <t>10,84; 13,46</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38170</t>
+          <t>39339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60912</t>
+          <t>63651</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6869</t>
+          <t>0; 6932</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 12750</t>
+          <t>0; 12919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1519,47 +1519,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29204; 48366</t>
+          <t>29826; 51162</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>220631; 265020</t>
+          <t>221479; 264006</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>258050; 304159</t>
+          <t>256635; 301811</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>170990; 215111</t>
+          <t>171365; 213473</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17094; 30479</t>
+          <t>17509; 32674</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>219338; 274510</t>
+          <t>219773; 275725</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>253722; 312421</t>
+          <t>253312; 314780</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169348; 220765</t>
+          <t>168373; 220946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49849; 74153</t>
+          <t>51740; 76790</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80322</t>
+          <t>84258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>34383</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>111989</t>
+          <t>118640</t>
         </is>
       </c>
     </row>
@@ -1722,52 +1722,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5191</t>
+          <t>0; 4263</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66550; 96288</t>
+          <t>69191; 100940</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24356; 42060</t>
+          <t>23150; 41817</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26653; 49456</t>
+          <t>26524; 50675</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50293; 80848</t>
+          <t>48149; 79006</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11046; 57767</t>
+          <t>25492; 43126</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22988; 45611</t>
+          <t>22942; 45226</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26571; 52539</t>
+          <t>27235; 52406</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48086; 83388</t>
+          <t>49401; 82077</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55077; 152015</t>
+          <t>100908; 136103</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>19248</t>
         </is>
       </c>
     </row>
@@ -1935,47 +1935,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5701; 18463</t>
+          <t>6371; 18898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2706; 12473</t>
+          <t>2650; 11872</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>994; 10162</t>
+          <t>1020; 9075</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1953; 9927</t>
+          <t>1144; 10512</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3578; 11077</t>
+          <t>4290; 12535</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2301; 12817</t>
+          <t>2285; 13036</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1009; 10786</t>
+          <t>984; 9557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2024; 11353</t>
+          <t>1922; 11048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11575; 25701</t>
+          <t>13073; 27925</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>135375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>190581</t>
+          <t>201539</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6964</t>
+          <t>0; 6903</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 12325</t>
+          <t>0; 11358</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4697</t>
+          <t>0; 5656</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>110799; 152098</t>
+          <t>115504; 155605</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>262575; 309304</t>
+          <t>261261; 309755</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>295850; 349342</t>
+          <t>295735; 350024</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>233960; 291863</t>
+          <t>236826; 288528</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30141; 82751</t>
+          <t>55451; 79875</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>256818; 314441</t>
+          <t>255092; 312903</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>292184; 359494</t>
+          <t>291979; 358893</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>235693; 299146</t>
+          <t>233824; 298760</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>128103; 227177</t>
+          <t>181402; 225195</t>
         </is>
       </c>
     </row>
